--- a/input/mapping/070. OCB_GOLD_TCKH_OPEX_DTL_HOP.xlsx
+++ b/input/mapping/070. OCB_GOLD_TCKH_OPEX_DTL_HOP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3707" documentId="13_ncr:1_{2EFA5FB6-F35E-4DC0-AF69-F056B4784F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA1D9702-14C3-45FC-A667-C19EB21A40F0}"/>
+  <xr:revisionPtr revIDLastSave="3709" documentId="13_ncr:1_{2EFA5FB6-F35E-4DC0-AF69-F056B4784F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E508B22-6839-4481-954A-C7F330371485}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -210,16 +210,9 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
--- ============================================================
--- OPEX_DTL
--- Load mode: DELETE theo ngày + INSERT (không phải TRUNCATE full)
--- Params: :DATADT (yyyyMMdd)
--- ============================================================
--- Xóa dữ liệu ngày cần chạy trước khi INSERT
 DELETE FROM OPEX_DTL
 WHERE MONTH_DATA = CAST(SUBSTR(:DATADT, 1, 6) AS INT)
   AND MONTH_DAY  = CAST(SUBSTR(:DATADT, 5, 4) AS INT);
--- INSERT dữ liệu ngày mới
 INSERT INTO OPEX_DTL
 SELECT
     t.MONTH_DATA,
@@ -246,8 +239,7 @@
 FROM PBCP_RESULT_FINAL t
 WHERE t.MONTH_DAY  = CAST(SUBSTR(:DATADT, 5, 4) AS INT)
   AND t.MONTH_DATA = CAST(SUBSTR(:DATADT, 1, 6) AS INT)
-  AND COALESCE(t.T_NARRATIVE, '') != 'Year End PL transfer'
-;</t>
+  AND COALESCE(t.T_NARRATIVE, '') != 'Year End PL transfer'</t>
   </si>
   <si>
     <t>[ CREATE OR REPLACE VIEW ]  UNION ALL 4 blocks  →  V_OPEX_DTL  |  Block 1 (g): V_OPEX_DTL_G — TRUC TIEP, AR_ID='1000', MA_PHONG_G cắt sau '.'/'*'  |  Block 2 (a): V_ENTRY_STMT_8830 — BHTG SAOKE, AR_ID='1000', T_AMT_PBCP đảo dấu  |  Block 3 (j): V_OPEX_DTL_ADJ_G LINE='8830' — điều chỉnh BHTG  |  Block 4 (k): V_OPEX_DTL_ADJ_G LINE&lt;&gt;'8830' — điều chỉnh khác</t>
@@ -12813,6 +12805,42 @@
     <xf numFmtId="0" fontId="8" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -12859,42 +12887,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13215,9 +13207,7 @@
     <xf numFmtId="0" fontId="23" fillId="23" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
@@ -19797,48 +19787,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="303" t="s">
+      <c r="A1" s="315" t="s">
         <v>1048</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-      <c r="G1" s="305"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="317"/>
     </row>
     <row r="2" spans="1:7" ht="43.5" customHeight="1">
-      <c r="A2" s="306" t="s">
+      <c r="A2" s="318" t="s">
         <v>1049</v>
       </c>
-      <c r="B2" s="307"/>
-      <c r="C2" s="307"/>
-      <c r="D2" s="307"/>
-      <c r="E2" s="307"/>
-      <c r="F2" s="307"/>
-      <c r="G2" s="308"/>
+      <c r="B2" s="319"/>
+      <c r="C2" s="319"/>
+      <c r="D2" s="319"/>
+      <c r="E2" s="319"/>
+      <c r="F2" s="319"/>
+      <c r="G2" s="320"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="309" t="s">
+      <c r="A3" s="321" t="s">
         <v>1050</v>
       </c>
-      <c r="B3" s="310"/>
-      <c r="C3" s="310"/>
-      <c r="D3" s="310"/>
-      <c r="E3" s="310"/>
-      <c r="F3" s="310"/>
-      <c r="G3" s="311"/>
+      <c r="B3" s="322"/>
+      <c r="C3" s="322"/>
+      <c r="D3" s="322"/>
+      <c r="E3" s="322"/>
+      <c r="F3" s="322"/>
+      <c r="G3" s="323"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="312" t="s">
+      <c r="A4" s="324" t="s">
         <v>1051</v>
       </c>
-      <c r="B4" s="312"/>
-      <c r="C4" s="312"/>
-      <c r="D4" s="312"/>
-      <c r="E4" s="312"/>
-      <c r="F4" s="312"/>
-      <c r="G4" s="312"/>
+      <c r="B4" s="324"/>
+      <c r="C4" s="324"/>
+      <c r="D4" s="324"/>
+      <c r="E4" s="324"/>
+      <c r="F4" s="324"/>
+      <c r="G4" s="324"/>
     </row>
     <row r="5" spans="1:7" ht="20.25" customHeight="1">
       <c r="A5" s="75" t="s">
@@ -20002,26 +19992,26 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="20.25" customHeight="1">
-      <c r="A12" s="313" t="s">
-        <v>179</v>
-      </c>
-      <c r="B12" s="314"/>
-      <c r="C12" s="314"/>
-      <c r="D12" s="314"/>
-      <c r="E12" s="314"/>
-      <c r="F12" s="314"/>
-      <c r="G12" s="315"/>
+      <c r="A12" s="325" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" s="326"/>
+      <c r="C12" s="326"/>
+      <c r="D12" s="326"/>
+      <c r="E12" s="326"/>
+      <c r="F12" s="326"/>
+      <c r="G12" s="327"/>
     </row>
     <row r="13" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A13" s="300" t="s">
+      <c r="A13" s="312" t="s">
         <v>1074</v>
       </c>
-      <c r="B13" s="301"/>
-      <c r="C13" s="301"/>
-      <c r="D13" s="301"/>
-      <c r="E13" s="301"/>
-      <c r="F13" s="301"/>
-      <c r="G13" s="302"/>
+      <c r="B13" s="313"/>
+      <c r="C13" s="313"/>
+      <c r="D13" s="313"/>
+      <c r="E13" s="313"/>
+      <c r="F13" s="313"/>
+      <c r="G13" s="314"/>
     </row>
     <row r="14" spans="1:7" ht="43.5">
       <c r="A14" s="80" t="s">
@@ -20047,15 +20037,15 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="30.75" customHeight="1">
-      <c r="A15" s="319" t="s">
+      <c r="A15" s="303" t="s">
         <v>1081</v>
       </c>
-      <c r="B15" s="320"/>
-      <c r="C15" s="320"/>
-      <c r="D15" s="320"/>
-      <c r="E15" s="320"/>
-      <c r="F15" s="320"/>
-      <c r="G15" s="321"/>
+      <c r="B15" s="304"/>
+      <c r="C15" s="304"/>
+      <c r="D15" s="304"/>
+      <c r="E15" s="304"/>
+      <c r="F15" s="304"/>
+      <c r="G15" s="305"/>
     </row>
     <row r="16" spans="1:7" ht="38.25">
       <c r="A16" s="84" t="s">
@@ -20541,15 +20531,15 @@
       </c>
     </row>
     <row r="37" spans="1:7" ht="24.75" customHeight="1">
-      <c r="A37" s="322" t="s">
+      <c r="A37" s="306" t="s">
         <v>1111</v>
       </c>
-      <c r="B37" s="323"/>
-      <c r="C37" s="323"/>
-      <c r="D37" s="323"/>
-      <c r="E37" s="323"/>
-      <c r="F37" s="323"/>
-      <c r="G37" s="324"/>
+      <c r="B37" s="307"/>
+      <c r="C37" s="307"/>
+      <c r="D37" s="307"/>
+      <c r="E37" s="307"/>
+      <c r="F37" s="307"/>
+      <c r="G37" s="308"/>
     </row>
     <row r="38" spans="1:7" ht="38.25">
       <c r="A38" s="84" t="s">
@@ -21035,15 +21025,15 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="26.25" customHeight="1">
-      <c r="A59" s="322" t="s">
+      <c r="A59" s="306" t="s">
         <v>1136</v>
       </c>
-      <c r="B59" s="323"/>
-      <c r="C59" s="323"/>
-      <c r="D59" s="323"/>
-      <c r="E59" s="323"/>
-      <c r="F59" s="323"/>
-      <c r="G59" s="324"/>
+      <c r="B59" s="307"/>
+      <c r="C59" s="307"/>
+      <c r="D59" s="307"/>
+      <c r="E59" s="307"/>
+      <c r="F59" s="307"/>
+      <c r="G59" s="308"/>
     </row>
     <row r="60" spans="1:7" ht="38.25">
       <c r="A60" s="84" t="s">
@@ -21529,15 +21519,15 @@
       </c>
     </row>
     <row r="81" spans="1:7" ht="29.25" customHeight="1">
-      <c r="A81" s="322" t="s">
+      <c r="A81" s="306" t="s">
         <v>1147</v>
       </c>
-      <c r="B81" s="323"/>
-      <c r="C81" s="323"/>
-      <c r="D81" s="323"/>
-      <c r="E81" s="323"/>
-      <c r="F81" s="323"/>
-      <c r="G81" s="324"/>
+      <c r="B81" s="307"/>
+      <c r="C81" s="307"/>
+      <c r="D81" s="307"/>
+      <c r="E81" s="307"/>
+      <c r="F81" s="307"/>
+      <c r="G81" s="308"/>
     </row>
     <row r="82" spans="1:7" ht="38.25">
       <c r="A82" s="84" t="s">
@@ -22023,26 +22013,26 @@
       </c>
     </row>
     <row r="103" spans="1:7">
-      <c r="A103" s="325" t="s">
-        <v>179</v>
-      </c>
-      <c r="B103" s="326"/>
-      <c r="C103" s="326"/>
-      <c r="D103" s="326"/>
-      <c r="E103" s="326"/>
-      <c r="F103" s="326"/>
-      <c r="G103" s="327"/>
+      <c r="A103" s="309" t="s">
+        <v>179</v>
+      </c>
+      <c r="B103" s="310"/>
+      <c r="C103" s="310"/>
+      <c r="D103" s="310"/>
+      <c r="E103" s="310"/>
+      <c r="F103" s="310"/>
+      <c r="G103" s="311"/>
     </row>
     <row r="104" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A104" s="316" t="s">
+      <c r="A104" s="300" t="s">
         <v>1150</v>
       </c>
-      <c r="B104" s="317"/>
-      <c r="C104" s="317"/>
-      <c r="D104" s="317"/>
-      <c r="E104" s="317"/>
-      <c r="F104" s="317"/>
-      <c r="G104" s="318"/>
+      <c r="B104" s="301"/>
+      <c r="C104" s="301"/>
+      <c r="D104" s="301"/>
+      <c r="E104" s="301"/>
+      <c r="F104" s="301"/>
+      <c r="G104" s="302"/>
     </row>
     <row r="105" spans="1:7" ht="63">
       <c r="A105" s="88" t="s">
@@ -22068,15 +22058,15 @@
       </c>
     </row>
     <row r="106" spans="1:7" ht="22.5" customHeight="1">
-      <c r="A106" s="316" t="s">
+      <c r="A106" s="300" t="s">
         <v>1155</v>
       </c>
-      <c r="B106" s="317"/>
-      <c r="C106" s="317"/>
-      <c r="D106" s="317"/>
-      <c r="E106" s="317"/>
-      <c r="F106" s="317"/>
-      <c r="G106" s="318"/>
+      <c r="B106" s="301"/>
+      <c r="C106" s="301"/>
+      <c r="D106" s="301"/>
+      <c r="E106" s="301"/>
+      <c r="F106" s="301"/>
+      <c r="G106" s="302"/>
     </row>
     <row r="107" spans="1:7" ht="63">
       <c r="A107" s="88" t="s">
@@ -22102,15 +22092,15 @@
       </c>
     </row>
     <row r="108" spans="1:7" ht="18.75" customHeight="1">
-      <c r="A108" s="316" t="s">
+      <c r="A108" s="300" t="s">
         <v>1158</v>
       </c>
-      <c r="B108" s="317"/>
-      <c r="C108" s="317"/>
-      <c r="D108" s="317"/>
-      <c r="E108" s="317"/>
-      <c r="F108" s="317"/>
-      <c r="G108" s="318"/>
+      <c r="B108" s="301"/>
+      <c r="C108" s="301"/>
+      <c r="D108" s="301"/>
+      <c r="E108" s="301"/>
+      <c r="F108" s="301"/>
+      <c r="G108" s="302"/>
     </row>
     <row r="109" spans="1:7" ht="38.25">
       <c r="A109" s="88" t="s">
@@ -22136,15 +22126,15 @@
       </c>
     </row>
     <row r="110" spans="1:7">
-      <c r="A110" s="316" t="s">
+      <c r="A110" s="300" t="s">
         <v>1162</v>
       </c>
-      <c r="B110" s="317"/>
-      <c r="C110" s="317"/>
-      <c r="D110" s="317"/>
-      <c r="E110" s="317"/>
-      <c r="F110" s="317"/>
-      <c r="G110" s="318"/>
+      <c r="B110" s="301"/>
+      <c r="C110" s="301"/>
+      <c r="D110" s="301"/>
+      <c r="E110" s="301"/>
+      <c r="F110" s="301"/>
+      <c r="G110" s="302"/>
     </row>
     <row r="111" spans="1:7" ht="50.25">
       <c r="A111" s="88" t="s">
@@ -22170,15 +22160,15 @@
       </c>
     </row>
     <row r="112" spans="1:7" ht="21" customHeight="1">
-      <c r="A112" s="316" t="s">
+      <c r="A112" s="300" t="s">
         <v>1166</v>
       </c>
-      <c r="B112" s="317"/>
-      <c r="C112" s="317"/>
-      <c r="D112" s="317"/>
-      <c r="E112" s="317"/>
-      <c r="F112" s="317"/>
-      <c r="G112" s="318"/>
+      <c r="B112" s="301"/>
+      <c r="C112" s="301"/>
+      <c r="D112" s="301"/>
+      <c r="E112" s="301"/>
+      <c r="F112" s="301"/>
+      <c r="G112" s="302"/>
     </row>
     <row r="113" spans="1:7" ht="75.75">
       <c r="A113" s="88" t="s">
@@ -22205,6 +22195,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A106:G106"/>
     <mergeCell ref="A108:G108"/>
     <mergeCell ref="A110:G110"/>
@@ -22215,12 +22211,6 @@
     <mergeCell ref="A81:G81"/>
     <mergeCell ref="A103:G103"/>
     <mergeCell ref="A104:G104"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26009,12 +25999,11 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
@@ -26027,11 +26016,12 @@
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26474,7 +26464,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.6">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -26508,13 +26498,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="303" t="s">
+      <c r="A1" s="315" t="s">
         <v>1402</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
       <c r="F1" s="362"/>
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1">
@@ -26686,23 +26676,23 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="32.450000000000003" customHeight="1">
-      <c r="A12" s="313" t="s">
-        <v>179</v>
-      </c>
-      <c r="B12" s="314"/>
-      <c r="C12" s="314"/>
-      <c r="D12" s="314"/>
-      <c r="E12" s="314"/>
+      <c r="A12" s="325" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" s="326"/>
+      <c r="C12" s="326"/>
+      <c r="D12" s="326"/>
+      <c r="E12" s="326"/>
       <c r="F12" s="366"/>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="300" t="s">
+      <c r="A13" s="312" t="s">
         <v>1074</v>
       </c>
-      <c r="B13" s="301"/>
-      <c r="C13" s="301"/>
-      <c r="D13" s="301"/>
-      <c r="E13" s="301"/>
+      <c r="B13" s="313"/>
+      <c r="C13" s="313"/>
+      <c r="D13" s="313"/>
+      <c r="E13" s="313"/>
       <c r="F13" s="361"/>
     </row>
     <row r="14" spans="1:6" ht="29.25">
@@ -27356,13 +27346,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A1" s="303" t="s">
+      <c r="A1" s="315" t="s">
         <v>1500</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
       <c r="F1" s="362"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1">
@@ -27964,13 +27954,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" customHeight="1">
-      <c r="A1" s="303" t="s">
+      <c r="A1" s="315" t="s">
         <v>1510</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
       <c r="F1" s="362"/>
     </row>
     <row r="2" spans="1:6" ht="40.5" customHeight="1">
@@ -28064,14 +28054,14 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="313" t="s">
-        <v>179</v>
-      </c>
-      <c r="B8" s="314"/>
-      <c r="C8" s="314"/>
-      <c r="D8" s="314"/>
-      <c r="E8" s="314"/>
-      <c r="F8" s="315"/>
+      <c r="A8" s="325" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="326"/>
+      <c r="C8" s="326"/>
+      <c r="D8" s="326"/>
+      <c r="E8" s="326"/>
+      <c r="F8" s="327"/>
     </row>
     <row r="9" spans="1:6" ht="14.45" customHeight="1">
       <c r="A9" s="343" t="s">
@@ -28234,13 +28224,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A1" s="303" t="s">
+      <c r="A1" s="315" t="s">
         <v>1527</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
       <c r="F1" s="362"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1">
@@ -28312,14 +28302,14 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="313" t="s">
-        <v>179</v>
-      </c>
-      <c r="B7" s="314"/>
-      <c r="C7" s="314"/>
-      <c r="D7" s="314"/>
-      <c r="E7" s="314"/>
-      <c r="F7" s="315"/>
+      <c r="A7" s="325" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="326"/>
+      <c r="C7" s="326"/>
+      <c r="D7" s="326"/>
+      <c r="E7" s="326"/>
+      <c r="F7" s="327"/>
     </row>
     <row r="8" spans="1:6" ht="14.45" customHeight="1">
       <c r="A8" s="343" t="s">
@@ -41345,14 +41335,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="303" t="s">
+      <c r="A1" s="315" t="s">
         <v>2112</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="305"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="317"/>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1">
       <c r="A2" s="363" t="s">
@@ -41445,14 +41435,14 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="325" t="s">
-        <v>179</v>
-      </c>
-      <c r="B8" s="326"/>
-      <c r="C8" s="326"/>
-      <c r="D8" s="326"/>
-      <c r="E8" s="326"/>
-      <c r="F8" s="327"/>
+      <c r="A8" s="309" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="310"/>
+      <c r="C8" s="310"/>
+      <c r="D8" s="310"/>
+      <c r="E8" s="310"/>
+      <c r="F8" s="311"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="373" t="s">
@@ -53004,27 +52994,27 @@
     <row r="222" ht="15"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A84:G84"/>
-    <mergeCell ref="A95:G95"/>
-    <mergeCell ref="A106:G106"/>
-    <mergeCell ref="A172:G172"/>
     <mergeCell ref="A183:G183"/>
     <mergeCell ref="A117:G117"/>
     <mergeCell ref="A128:G128"/>
     <mergeCell ref="A139:G139"/>
     <mergeCell ref="A150:G150"/>
     <mergeCell ref="A161:G161"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A84:G84"/>
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A106:G106"/>
+    <mergeCell ref="A172:G172"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="A6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -55679,16 +55669,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -55697,7 +55677,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -55869,14 +55849,24 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD798580-E728-431C-8751-C1407BFA2546}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{169E7700-53E3-4F58-8B2B-1DA330E4A6F9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{169E7700-53E3-4F58-8B2B-1DA330E4A6F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C75CC7-3264-49B9-A7E5-314B8F17DD35}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88C75CC7-3264-49B9-A7E5-314B8F17DD35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD798580-E728-431C-8751-C1407BFA2546}"/>
 </file>